--- a/healthcare_forms/046_eating_disorder_screener_form--healthcare_forms.xlsx
+++ b/healthcare_forms/046_eating_disorder_screener_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1075,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>purging</t>
+          <t>eating_very_fast</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Purging</t>
+          <t>Eating very fast</t>
         </is>
       </c>
     </row>
@@ -1380,29 +1380,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>eating_very_fast</t>
+          <t>eating_very_little</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Eating very fast</t>
+          <t>Eating very little</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>eating_behaviors_choices</t>
+          <t>food_preferences_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>eating_very_little</t>
+          <t>fruits</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eating very little</t>
+          <t>Fruits</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>fruits</t>
+          <t>vegetables</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fruits</t>
+          <t>Vegetables</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>vegetables</t>
+          <t>grains</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vegetables</t>
+          <t>Grains</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>grains</t>
+          <t>meat</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Grains</t>
+          <t>Meat</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>meat</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Meat</t>
+          <t>Dairy</t>
         </is>
       </c>
     </row>
@@ -1482,29 +1482,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>dairy</t>
+          <t>fats/oils</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Fats/Oils</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>food_preferences_choices</t>
+          <t>food_aversions_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>fats/oils</t>
+          <t>fruits</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fats/Oils</t>
+          <t>Fruits</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>fruits</t>
+          <t>vegetables</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fruits</t>
+          <t>Vegetables</t>
         </is>
       </c>
     </row>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>vegetables</t>
+          <t>grains</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vegetables</t>
+          <t>Grains</t>
         </is>
       </c>
     </row>
@@ -1550,12 +1550,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>grains</t>
+          <t>meat</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Grains</t>
+          <t>Meat</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>meat</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Meat</t>
+          <t>Dairy</t>
         </is>
       </c>
     </row>
@@ -1584,29 +1584,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>dairy</t>
+          <t>fats/oils</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Fats/Oils</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>food_aversions_choices</t>
+          <t>eating_habits_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>fats/oils</t>
+          <t>eating_in_response_to_boredom</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fats/Oils</t>
+          <t>Eating in response to boredom</t>
         </is>
       </c>
     </row>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>eating_in_response_to_boredom</t>
+          <t>eating_in_response_to_stress</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Eating in response to boredom</t>
+          <t>Eating in response to stress</t>
         </is>
       </c>
     </row>
@@ -1635,12 +1635,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>eating_in_response_to_stress</t>
+          <t>eating_to_soothe_emotions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eating in response to stress</t>
+          <t>Eating to soothe emotions</t>
         </is>
       </c>
     </row>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>eating_to_soothe_emotions</t>
+          <t>eating_when_not_hungry</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eating to soothe emotions</t>
+          <t>Eating when not hungry</t>
         </is>
       </c>
     </row>
@@ -1669,12 +1669,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>eating_when_not_hungry</t>
+          <t>eating_when_hungry</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eating when not hungry</t>
+          <t>Eating when hungry</t>
         </is>
       </c>
     </row>
@@ -1686,12 +1686,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>eating_when_hungry</t>
+          <t>eating_in_secret</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eating when hungry</t>
+          <t>Eating in secret</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>eating_in_secret</t>
+          <t>eating_very_fast</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eating in secret</t>
+          <t>Eating very fast</t>
         </is>
       </c>
     </row>
@@ -1720,29 +1720,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>eating_very_fast</t>
+          <t>eating_very_little</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Eating very fast</t>
+          <t>Eating very little</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>eating_habits_choices</t>
+          <t>food_control_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>eating_very_little</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Eating very little</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -1771,12 +1771,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>somewhat</t>
+          <t>some_control</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Somewhat</t>
+          <t>Some control</t>
         </is>
       </c>
     </row>
@@ -1788,12 +1788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>some_control</t>
+          <t>a_little_control</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Some control</t>
+          <t>A little control</t>
         </is>
       </c>
     </row>
@@ -1805,12 +1805,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>a_little_control</t>
+          <t>quite_a_bit_of_control</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>A little control</t>
+          <t>Quite a bit of control</t>
         </is>
       </c>
     </row>
@@ -1822,12 +1822,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>quite_a_bit_of_control</t>
+          <t>a_lot_of_control</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Quite a bit of control</t>
+          <t>A lot of control</t>
         </is>
       </c>
     </row>
@@ -1839,29 +1839,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>a_lot_of_control</t>
+          <t>almost_complete_control</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>A lot of control</t>
+          <t>Almost complete control</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>food_control_choices</t>
+          <t>food_avoidance_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>almost_complete_control</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Almost complete control</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>some</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Some</t>
         </is>
       </c>
     </row>
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>some</t>
+          <t>a_lot</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Some</t>
+          <t>A lot</t>
         </is>
       </c>
     </row>
@@ -1907,29 +1907,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>a_lot</t>
+          <t>almost_none</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>A lot</t>
+          <t>Almost none</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>food_avoidance_choices</t>
+          <t>eating_avoidance_reasons_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>almost_none</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Almost none</t>
+          <t>Weight</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>body_image</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Weight</t>
+          <t>Body image</t>
         </is>
       </c>
     </row>
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>body_image</t>
+          <t>fear_of_choking</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Body image</t>
+          <t>Fear of choking</t>
         </is>
       </c>
     </row>
@@ -1975,12 +1975,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>fear_of_choking</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fear of choking</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1992,29 +1992,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>fear_of_vomiting</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fear of vomiting</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>eating_avoidance_reasons_choices</t>
+          <t>body_image_distortion_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>fear_of_vomiting</t>
+          <t>body_fat</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fear of vomiting</t>
+          <t>Body fat</t>
         </is>
       </c>
     </row>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>body_fat</t>
+          <t>body_shape</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Body fat</t>
+          <t>Body shape</t>
         </is>
       </c>
     </row>
@@ -2043,12 +2043,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>body_shape</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Body shape</t>
+          <t>Weight</t>
         </is>
       </c>
     </row>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>muscle_mass</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Weight</t>
+          <t>Muscle mass</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>muscle_mass</t>
+          <t>body_strength</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Muscle mass</t>
+          <t>Body strength</t>
         </is>
       </c>
     </row>
@@ -2094,29 +2094,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>body_strength</t>
+          <t>body_appearance</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Body strength</t>
+          <t>Body appearance</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>body_image_distortion_choices</t>
+          <t>emotional_states_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>body_appearance</t>
+          <t>fear_of_failure</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Body appearance</t>
+          <t>Fear of failure</t>
         </is>
       </c>
     </row>
@@ -2128,12 +2128,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>fear_of_failure</t>
+          <t>shame</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fear of failure</t>
+          <t>Shame</t>
         </is>
       </c>
     </row>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>shame</t>
+          <t>anger</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Shame</t>
+          <t>Anger</t>
         </is>
       </c>
     </row>
@@ -2162,12 +2162,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>anger</t>
+          <t>fear_of_weight_gain</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Anger</t>
+          <t>Fear of weight gain</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>fear_of_weight_gain</t>
+          <t>anxiety</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fear of weight gain</t>
+          <t>Anxiety</t>
         </is>
       </c>
     </row>
@@ -2196,12 +2196,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>anxiety</t>
+          <t>sadness</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Anxiety</t>
+          <t>Sadness</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>sadness</t>
+          <t>fear_of_loss</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sadness</t>
+          <t>Fear of loss</t>
         </is>
       </c>
     </row>
@@ -2230,12 +2230,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>fear_of_loss</t>
+          <t>fear_of_rejection</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fear of loss</t>
+          <t>Fear of rejection</t>
         </is>
       </c>
     </row>
@@ -2247,29 +2247,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>fear_of_rejection</t>
+          <t>fear_of_success</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fear of rejection</t>
+          <t>Fear of success</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>emotional_states_choices</t>
+          <t>food_refusal_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>fear_of_success</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fear of success</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2281,12 +2281,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>some</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Some</t>
         </is>
       </c>
     </row>
@@ -2298,12 +2298,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>some</t>
+          <t>a_lot</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Some</t>
+          <t>A lot</t>
         </is>
       </c>
     </row>
@@ -2315,29 +2315,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>a_lot</t>
+          <t>almost_none</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>A lot</t>
+          <t>Almost none</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>food_refusal_choices</t>
+          <t>eating_refusal_reasons_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>almost_none</t>
+          <t>fear_of_choking</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Almost none</t>
+          <t>Fear of choking</t>
         </is>
       </c>
     </row>
@@ -2349,12 +2349,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>fear_of_choking</t>
+          <t>fear_of_vomiting</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fear of choking</t>
+          <t>Fear of vomiting</t>
         </is>
       </c>
     </row>
@@ -2366,12 +2366,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>fear_of_vomiting</t>
+          <t>fear_of_losing_control</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Fear of vomiting</t>
+          <t>Fear of losing control</t>
         </is>
       </c>
     </row>
@@ -2383,29 +2383,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>fear_of_losing_control</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fear of losing control</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>eating_refusal_reasons_choices</t>
+          <t>weight_concerns_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>weight_gain</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Weight gain</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>weight_gain</t>
+          <t>weight_loss</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Weight gain</t>
+          <t>Weight loss</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>weight_loss</t>
+          <t>body_fat</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Weight loss</t>
+          <t>Body fat</t>
         </is>
       </c>
     </row>
@@ -2451,29 +2451,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>body_fat</t>
+          <t>weight_distribution</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Body fat</t>
+          <t>Weight distribution</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>weight_concerns_choices</t>
+          <t>weight_preoccupation_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>weight_distribution</t>
+          <t>weight_gain</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Weight distribution</t>
+          <t>Weight gain</t>
         </is>
       </c>
     </row>
@@ -2485,12 +2485,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>weight_gain</t>
+          <t>weight_loss</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Weight gain</t>
+          <t>Weight loss</t>
         </is>
       </c>
     </row>
@@ -2502,12 +2502,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>weight_loss</t>
+          <t>body_fat</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Weight loss</t>
+          <t>Body fat</t>
         </is>
       </c>
     </row>
@@ -2519,27 +2519,10 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>body_fat</t>
+          <t>weight_distribution</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
-        <is>
-          <t>Body fat</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>weight_preoccupation_choices</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>weight_distribution</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
         <is>
           <t>Weight distribution</t>
         </is>
